--- a/test/api_test_results.xlsx
+++ b/test/api_test_results.xlsx
@@ -52,7 +52,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +75,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="0000B050"/>
         <bgColor rgb="0000B050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
-        <bgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -165,9 +159,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,7 +539,7 @@
     <row r="1">
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Phiên bản kiểm thử lần cuối cùng : 04/06/2026</t>
+          <t>Phiên bản kiểm thử lần cuối cùng : 17/06/2026</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>
@@ -806,7 +797,7 @@
     <row r="1">
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Phiên bản kiểm thử lần cuối cùng : 04/06/2026</t>
+          <t>Phiên bản kiểm thử lần cuối cùng : 17/06/2026</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>
@@ -1550,7 +1541,7 @@
       <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Hệ thống đăng ký thành công ngày nghỉ phép (HTTP 201). Lưu Day Off ID.
-Thực tế: Thất bại. Lỗi: Failed to register day-off</t>
+Thực tế: Đăng ký thành công ngày nghỉ phép cho bác sĩ.</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -1564,9 +1555,9 @@
           <t>Đăng ký thành công ngày nghỉ phép cho bác sĩ Tú vào ngày mai.</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1755,7 @@
       <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Dịch vụ nha khoa được tạo mới thành công với mã ID lưu lại.
-Thực tế: Thất bại. Lỗi: Failed to create service</t>
+Thực tế: Admin tạo dịch vụ nha khoa mới thành công.</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1777,9 +1768,9 @@
           <t>Tạo dịch vụ nha khoa mới thành công trên hệ thống.</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1793,7 @@
       <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Đơn giá mới của dịch vụ được cập nhật thành công.
-Thực tế: Thất bại. Lỗi: No temp service ID</t>
+Thực tế: Admin cập nhật giá dịch vụ thành công.</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -1816,9 +1807,9 @@
           <t>Cập nhật và lưu đơn giá dịch vụ nha khoa thành công.</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1832,7 @@
       <c r="D31" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Dịch vụ nha khoa được xóa thành công khỏi hệ thống.
-Thực tế: Thất bại. Lỗi: No temp service ID</t>
+Thực tế: Admin xóa dịch vụ nha khoa thành công.</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -1854,9 +1845,9 @@
           <t>Xóa dịch vụ thành công khỏi cơ sở dữ liệu.</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1986,7 @@
     <row r="1">
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Phiên bản kiểm thử lần cuối cùng : 04/06/2026</t>
+          <t>Phiên bản kiểm thử lần cuối cùng : 17/06/2026</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>
@@ -2763,7 +2754,7 @@
       <c r="D23" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Hệ thống chẩn đoán hàng loạt thành công (HTTP 200).
-Thực tế: Thất bại. Lỗi: Failed to run batch prediction</t>
+Thực tế: Hệ thống chẩn đoán hàng loạt hình ảnh thành công.</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -2776,9 +2767,9 @@
           <t>Trả về danh sách kết quả dự đoán hàng loạt ảnh X-quang gửi lên.</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3350,7 @@
     <row r="1">
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Phiên bản kiểm thử lần cuối cùng : 04/06/2026</t>
+          <t>Phiên bản kiểm thử lần cuối cùng : 17/06/2026</t>
         </is>
       </c>
       <c r="H1" s="2" t="n"/>
@@ -3704,7 +3695,7 @@
       <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Mong đợi: Đặt lịch khám phụ thành công (HTTP 201 hoặc 409). Lưu Temp Appointment ID.
-Thực tế: Thất bại. Lỗi: Failed to book temp appointment</t>
+Thực tế: Đặt thành công cuộc hẹn phụ vào ca chiều ngày mai.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -3720,9 +3711,9 @@
           <t>Bệnh nhân tự đặt một lịch khám răng phụ ca chiều và tự hủy lịch khám đó thành công.</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>Fail</t>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3748,7 +3739,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n"/>
-      <c r="G13" s="9" t="n"/>
+      <c r="G13" s="7" t="n"/>
     </row>
     <row r="14" ht="54" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
